--- a/results/log_pv_cap/log_pv_cap_capacities_effects.xlsx
+++ b/results/log_pv_cap/log_pv_cap_capacities_effects.xlsx
@@ -511,679 +511,679 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_gdp_cap</t>
+          <t>Households per capita</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-6.336</t>
+          <t>-44.015</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.197</t>
+          <t>-3.943</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-6.140</t>
+          <t>-40.073</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.549</t>
+          <t>-6.222</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>-3.904</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.447</t>
+          <t>-2.318</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.325</t>
+          <t>-4.468</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.113</t>
+          <t>-3.940</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.212</t>
+          <t>-0.528</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.217</t>
+          <t>-6.593</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.045</t>
+          <t>-4.086</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.172</t>
+          <t>-2.507</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>-4.484</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>-4.169</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.315</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>-4.252</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.150</t>
+          <t>-4.159</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>-0.093</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_fcapacity</t>
+          <t>GDP per capita</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-29.392</t>
+          <t>-7.678</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.018</t>
+          <t>-0.329</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-34.411</t>
+          <t>-7.349</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.741</t>
+          <t>-1.067</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>-0.221</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>-0.845</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>-0.726</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>-0.209</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.575</t>
+          <t>-0.516</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11.561</t>
+          <t>-0.115</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.402</t>
+          <t>-0.071</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9.160</t>
+          <t>-0.044</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8.221</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>5.552</t>
+          <t>0.034</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8.040</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.695</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hcapacity</t>
+          <t>Firms per capita</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-41.181</t>
+          <t>-32.365</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.891</t>
+          <t>7.162</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-39.290</t>
+          <t>-39.527</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.974</t>
+          <t>1.689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.855</t>
+          <t>6.309</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.120</t>
+          <t>-4.621</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.669</t>
+          <t>2.267</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.891</t>
+          <t>6.297</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.779</t>
+          <t>-4.030</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-9.130</t>
+          <t>6.101</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-1.897</t>
+          <t>3.781</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-7.234</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-3.026</t>
+          <t>9.571</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-2.044</t>
+          <t>8.898</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.982</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-2.492</t>
+          <t>9.989</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-2.075</t>
+          <t>9.769</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.417</t>
+          <t>0.220</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_acapacity</t>
+          <t>Firm assets per capita</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.232</t>
+          <t>10.073</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.034</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.201</t>
+          <t>10.040</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.216</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>0.036</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.017</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.034</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.902</t>
+          <t>14.313</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.556</t>
+          <t>-0.074</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.458</t>
+          <t>14.387</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.427</t>
+          <t>5.868</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.537</t>
+          <t>5.454</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.453</t>
+          <t>5.346</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.376</t>
+          <t>4.745</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.397</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.498</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-1.899</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>3.203</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>2.978</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.225</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>3.339</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2.162</t>
+          <t>3.266</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.073</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>2.374</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.997</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1.377</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>1.020</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.993</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.993</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.610</t>
+          <t>1.603</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.993</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>1.078</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>1.002</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1.024</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>1.002</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.023</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-1.622</t>
+          <t>-1.925</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-1.640</t>
+          <t>-1.924</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.195</t>
+          <t>-0.319</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.103</t>
+          <t>-0.137</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.092</t>
+          <t>-0.181</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-0.359</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.291</t>
+          <t>-0.328</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.077</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.061</t>
+          <t>-0.049</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.058</t>
+          <t>-0.084</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.078</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.075</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.002</t>
         </is>
       </c>
     </row>
